--- a/__post ipo univ.xlsx
+++ b/__post ipo univ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bloomberg\Documents\ssh_project\post_ipo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3345873-5A4D-4205-BF13-9495DC39EF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146858FA-85CF-4A57-A78F-16EE8334C35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0DC4A533-A1D4-4E27-8861-6ABA3CFD02B2}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="442">
   <si>
     <t>Symbol</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1374,6 +1374,14 @@
   </si>
   <si>
     <t>A0011A0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A0008Z0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에스엔시스</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -23170,7 +23178,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="B2:E151"/>
+  <dimension ref="B2:E152"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
@@ -25280,6 +25288,14 @@
         <v>20000</v>
       </c>
     </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B152" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
